--- a/docs/data/jp/xlsx/5885.xlsx
+++ b/docs/data/jp/xlsx/5885.xlsx
@@ -228,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -350,6 +350,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -759,7 +762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC134"/>
+  <dimension ref="A1:AC140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4203,11 +4206,11 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 (2026.10.23)</t>
+          <t>현재 주가 (2026.10.26)</t>
         </is>
       </c>
       <c r="B47" s="29" t="n">
-        <v>3130</v>
+        <v>3170</v>
       </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
@@ -5444,7 +5447,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉 2026.10.23</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5693,456 +5696,495 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>937.576</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>1084.481</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>845.865</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>969.576</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>2310.711</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>1124.408</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>888.663</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>646.727</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>1551.798</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>1256.871</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>1757.972</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>988.879</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>622.772</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>845.865</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>888.663</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>1757.972</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>229.734</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>288.347</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>316.799</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>279.636</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>435.195</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>319.806</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>302.935</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>302.12</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>583.17</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>318.893</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>531.458</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>553.0309999999999</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>208.077</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>316.799</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>302.935</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>531.458</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>79.977</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>97.22</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>106.657</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>103.293</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>112.997</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>118.688</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>162.684</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>135.206</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>136.338</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>121.374</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>225.313</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>146.225</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>129.243</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>106.657</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>162.684</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>225.313</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>149.756</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>191.128</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>210.142</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>176.342</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>322.198</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>201.118</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>140.252</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>166.914</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>446.831</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>197.52</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>306.145</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>406.806</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>78.833</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>210.142</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>140.252</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>306.145</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>외환차익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>-0.84</v>
+        <v>79.977</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>13.574</v>
+        <v>97.22</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>-9.25</v>
+        <v>106.657</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>0</v>
+        <v>103.293</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>0</v>
+        <v>112.997</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>0</v>
+        <v>118.688</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>0</v>
+        <v>162.684</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>22.907</v>
+        <v>135.206</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>4.181</v>
+        <v>136.338</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>3.626</v>
+        <v>121.374</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>10.974</v>
+        <v>225.313</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>2.453</v>
+        <v>146.225</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>2.256</v>
+        <v>129.243</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>-9.25</v>
+        <v>106.657</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>0</v>
+        <v>162.684</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>10.974</v>
+        <v>225.313</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>이자수익</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="22" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="E84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>1.035</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>2.663</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>4.591</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>9.954000000000001</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>8.202999999999999</v>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L84" s="22" t="n">
-        <v>3.127</v>
-      </c>
-      <c r="M84" s="22" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="N84" s="22" t="n">
-        <v>2.854</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>9.954000000000001</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>0.003</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>149.756</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>191.128</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>210.142</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>176.342</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>322.198</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>201.118</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>140.252</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>166.914</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>446.831</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>197.52</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>306.145</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>406.806</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>78.833</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>210.142</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>140.252</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>306.145</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="D85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>0.503</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="N85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" s="22" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>0.503</v>
-      </c>
-      <c r="X85" s="22" t="n">
-        <v>0.285</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>영업외수익 합계</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>-0.743</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>13.59</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>-8.763</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>2.675</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>4.591</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>10.457</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>31.139</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>4.183</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>6.754</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>11.261</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>5.307</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>-8.763</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>10.457</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>11.261</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용</t>
+          <t>외환차익</t>
         </is>
       </c>
       <c r="C87" s="22" t="n">
-        <v>0</v>
+        <v>-0.84</v>
       </c>
       <c r="D87" s="22" t="n">
-        <v>0</v>
+        <v>13.574</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>0</v>
+        <v>-9.25</v>
       </c>
       <c r="F87" s="22" t="n">
         <v>0</v>
@@ -6156,94 +6198,115 @@
       <c r="I87" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="J87" s="22" t="n">
+        <v>22.907</v>
+      </c>
+      <c r="K87" s="22" t="n">
+        <v>4.181</v>
+      </c>
+      <c r="L87" s="22" t="n">
+        <v>3.626</v>
+      </c>
+      <c r="M87" s="22" t="n">
+        <v>10.974</v>
+      </c>
+      <c r="N87" s="22" t="n">
+        <v>2.453</v>
+      </c>
       <c r="U87" s="22" t="n">
-        <v>3.729</v>
+        <v>2.256</v>
       </c>
       <c r="V87" s="22" t="n">
-        <v>0</v>
+        <v>-9.25</v>
       </c>
       <c r="W87" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="X87" s="22" t="n">
+        <v>10.974</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="C88" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="E88" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>13.242</v>
+        <v>1.035</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>-7.954</v>
+        <v>2.663</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>25.2</v>
+        <v>4.591</v>
       </c>
       <c r="I88" s="22" t="n">
-        <v>32.288</v>
+        <v>9.954000000000001</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>0</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="K88" s="22" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>0</v>
+        <v>3.127</v>
       </c>
       <c r="M88" s="22" t="n">
-        <v>0</v>
+        <v>0.003</v>
+      </c>
+      <c r="N88" s="22" t="n">
+        <v>2.854</v>
       </c>
       <c r="V88" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W88" s="22" t="n">
-        <v>32.288</v>
+        <v>9.954000000000001</v>
       </c>
       <c r="X88" s="22" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
-        <v>0</v>
+        <v>0.097</v>
       </c>
       <c r="D89" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E89" s="22" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="F89" s="22" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="G89" s="22" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="H89" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F89" s="22" t="n">
-        <v>13.242</v>
-      </c>
-      <c r="G89" s="22" t="n">
-        <v>-7.954</v>
-      </c>
-      <c r="H89" s="22" t="n">
-        <v>25.2</v>
-      </c>
       <c r="I89" s="22" t="n">
-        <v>32.288</v>
+        <v>0.503</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="K89" s="22" t="n">
         <v>0</v>
@@ -6252,1334 +6315,1500 @@
         <v>0</v>
       </c>
       <c r="M89" s="22" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="N89" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U89" s="22" t="n">
-        <v>3.729</v>
+        <v>0.096</v>
       </c>
       <c r="V89" s="22" t="n">
-        <v>0</v>
+        <v>0.486</v>
       </c>
       <c r="W89" s="22" t="n">
-        <v>32.288</v>
+        <v>0.503</v>
       </c>
       <c r="X89" s="22" t="n">
-        <v>0</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C90" s="12" t="n">
-        <v>149.013</v>
-      </c>
-      <c r="D90" s="12" t="n">
-        <v>204.718</v>
-      </c>
-      <c r="E90" s="12" t="n">
-        <v>201.379</v>
-      </c>
-      <c r="F90" s="12" t="n">
-        <v>164.331</v>
-      </c>
-      <c r="G90" s="12" t="n">
-        <v>332.827</v>
-      </c>
-      <c r="H90" s="12" t="n">
-        <v>180.509</v>
-      </c>
-      <c r="I90" s="12" t="n">
-        <v>118.42</v>
-      </c>
-      <c r="J90" s="12" t="n">
-        <v>198.054</v>
-      </c>
-      <c r="K90" s="12" t="n">
-        <v>451.014</v>
-      </c>
-      <c r="L90" s="12" t="n">
-        <v>204.274</v>
-      </c>
-      <c r="M90" s="12" t="n">
-        <v>317.406</v>
-      </c>
-      <c r="N90" s="12" t="n">
-        <v>412.113</v>
-      </c>
-      <c r="U90" s="12" t="n">
-        <v>77.456</v>
-      </c>
-      <c r="V90" s="12" t="n">
-        <v>201.379</v>
-      </c>
-      <c r="W90" s="12" t="n">
-        <v>118.42</v>
-      </c>
-      <c r="X90" s="12" t="n">
-        <v>317.406</v>
+      <c r="A90" s="20" t="inlineStr">
+        <is>
+          <t>영업외수익 합계</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="n">
+        <v>-0.743</v>
+      </c>
+      <c r="D90" s="22" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="E90" s="22" t="n">
+        <v>-8.763</v>
+      </c>
+      <c r="F90" s="22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G90" s="22" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="H90" s="22" t="n">
+        <v>4.591</v>
+      </c>
+      <c r="I90" s="22" t="n">
+        <v>10.457</v>
+      </c>
+      <c r="J90" s="22" t="n">
+        <v>31.139</v>
+      </c>
+      <c r="K90" s="22" t="n">
+        <v>4.183</v>
+      </c>
+      <c r="L90" s="22" t="n">
+        <v>6.754</v>
+      </c>
+      <c r="M90" s="22" t="n">
+        <v>11.261</v>
+      </c>
+      <c r="N90" s="22" t="n">
+        <v>5.307</v>
+      </c>
+      <c r="U90" s="22" t="n">
+        <v>2.353</v>
+      </c>
+      <c r="V90" s="22" t="n">
+        <v>-8.763</v>
+      </c>
+      <c r="W90" s="22" t="n">
+        <v>10.457</v>
+      </c>
+      <c r="X90" s="22" t="n">
+        <v>11.261</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
-        </is>
+          <t>상장 관련 비용</t>
+        </is>
+      </c>
+      <c r="C91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="E91" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="F91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="U91" s="22" t="n">
-        <v>0</v>
+        <v>3.729</v>
       </c>
       <c r="V91" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="W91" s="22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
-        </is>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="E92" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="U92" s="22" t="n">
+      <c r="F92" s="22" t="n">
+        <v>13.242</v>
+      </c>
+      <c r="G92" s="22" t="n">
+        <v>-7.954</v>
+      </c>
+      <c r="H92" s="22" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I92" s="22" t="n">
+        <v>32.288</v>
+      </c>
+      <c r="J92" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V92" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="W92" s="22" t="n">
+        <v>32.288</v>
+      </c>
+      <c r="X92" s="22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="inlineStr">
+      <c r="A93" s="20" t="inlineStr">
+        <is>
+          <t>영업외비용 합계</t>
+        </is>
+      </c>
+      <c r="C93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="22" t="n">
+        <v>13.242</v>
+      </c>
+      <c r="G93" s="22" t="n">
+        <v>-7.954</v>
+      </c>
+      <c r="H93" s="22" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I93" s="22" t="n">
+        <v>32.288</v>
+      </c>
+      <c r="J93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" s="22" t="n">
+        <v>3.729</v>
+      </c>
+      <c r="V93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" s="22" t="n">
+        <v>32.288</v>
+      </c>
+      <c r="X93" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="n">
+        <v>149.013</v>
+      </c>
+      <c r="D94" s="12" t="n">
+        <v>204.718</v>
+      </c>
+      <c r="E94" s="12" t="n">
+        <v>201.379</v>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>164.331</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>332.827</v>
+      </c>
+      <c r="H94" s="12" t="n">
+        <v>180.509</v>
+      </c>
+      <c r="I94" s="12" t="n">
+        <v>118.42</v>
+      </c>
+      <c r="J94" s="12" t="n">
+        <v>198.054</v>
+      </c>
+      <c r="K94" s="12" t="n">
+        <v>451.014</v>
+      </c>
+      <c r="L94" s="12" t="n">
+        <v>204.274</v>
+      </c>
+      <c r="M94" s="12" t="n">
+        <v>317.406</v>
+      </c>
+      <c r="N94" s="12" t="n">
+        <v>412.113</v>
+      </c>
+      <c r="U94" s="12" t="n">
+        <v>77.456</v>
+      </c>
+      <c r="V94" s="12" t="n">
+        <v>201.379</v>
+      </c>
+      <c r="W94" s="12" t="n">
+        <v>118.42</v>
+      </c>
+      <c r="X94" s="12" t="n">
+        <v>317.406</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G95" s="17">
+        <f>IF(OR(G94="",C94=""),"",IF(C94&lt;=0,"",IFERROR(G94/C94-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H95" s="17">
+        <f>IF(OR(H94="",D94=""),"",IF(D94&lt;=0,"",IFERROR(H94/D94-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I95" s="17">
+        <f>IF(OR(I94="",E94=""),"",IF(E94&lt;=0,"",IFERROR(I94/E94-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J95" s="17">
+        <f>IF(OR(J94="",F94=""),"",IF(F94&lt;=0,"",IFERROR(J94/F94-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K95" s="17">
+        <f>IF(OR(K94="",G94=""),"",IF(G94&lt;=0,"",IFERROR(K94/G94-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L95" s="17">
+        <f>IF(OR(L94="",H94=""),"",IF(H94&lt;=0,"",IFERROR(L94/H94-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M95" s="17">
+        <f>IF(OR(M94="",I94=""),"",IF(I94&lt;=0,"",IFERROR(M94/I94-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N95" s="17">
+        <f>IF(OR(N94="",J94=""),"",IF(J94&lt;=0,"",IFERROR(N94/J94-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U95" s="17">
+        <f>IF(OR(U94="",T94=""),"",IF(T94&lt;=0,"",IFERROR(U94/T94-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V95" s="17">
+        <f>IF(OR(V94="",U94=""),"",IF(U94&lt;=0,"",IFERROR(V94/U94-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W95" s="17">
+        <f>IF(OR(W94="",V94=""),"",IF(V94&lt;=0,"",IFERROR(W94/V94-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X95" s="17">
+        <f>IF(OR(X94="",W94=""),"",IF(W94&lt;=0,"",IFERROR(X94/W94-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>고정자산 제각손실</t>
+        </is>
+      </c>
+      <c r="E96" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="E97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="C93" s="12" t="n">
+      <c r="C98" s="12" t="n">
         <v>149.013</v>
       </c>
-      <c r="D93" s="12" t="n">
+      <c r="D98" s="12" t="n">
         <v>204.718</v>
       </c>
-      <c r="E93" s="12" t="n">
+      <c r="E98" s="12" t="n">
         <v>201.379</v>
       </c>
-      <c r="F93" s="12" t="n">
+      <c r="F98" s="12" t="n">
         <v>164.331</v>
       </c>
-      <c r="G93" s="12" t="n">
+      <c r="G98" s="12" t="n">
         <v>332.827</v>
       </c>
-      <c r="H93" s="12" t="n">
+      <c r="H98" s="12" t="n">
         <v>180.509</v>
       </c>
-      <c r="I93" s="12" t="n">
+      <c r="I98" s="12" t="n">
         <v>118.42</v>
       </c>
-      <c r="J93" s="12" t="n">
+      <c r="J98" s="12" t="n">
         <v>198.054</v>
       </c>
-      <c r="K93" s="12" t="n">
+      <c r="K98" s="12" t="n">
         <v>451.014</v>
       </c>
-      <c r="L93" s="12" t="n">
+      <c r="L98" s="12" t="n">
         <v>204.274</v>
       </c>
-      <c r="M93" s="12" t="n">
+      <c r="M98" s="12" t="n">
         <v>317.406</v>
       </c>
-      <c r="N93" s="12" t="n">
+      <c r="N98" s="12" t="n">
         <v>412.113</v>
       </c>
-      <c r="U93" s="12" t="n">
+      <c r="U98" s="12" t="n">
         <v>77.45699999999999</v>
       </c>
-      <c r="V93" s="12" t="n">
+      <c r="V98" s="12" t="n">
         <v>201.379</v>
       </c>
-      <c r="W93" s="12" t="n">
+      <c r="W98" s="12" t="n">
         <v>118.42</v>
       </c>
-      <c r="X93" s="12" t="n">
+      <c r="X98" s="12" t="n">
         <v>317.406</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="20" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="20" t="inlineStr">
         <is>
           <t>법인세 등</t>
         </is>
       </c>
-      <c r="C94" s="22" t="n">
+      <c r="C99" s="22" t="n">
         <v>45.613</v>
       </c>
-      <c r="D94" s="22" t="n">
+      <c r="D99" s="22" t="n">
         <v>62.666</v>
       </c>
-      <c r="E94" s="22" t="n">
+      <c r="E99" s="22" t="n">
         <v>82.107</v>
       </c>
-      <c r="F94" s="22" t="n">
+      <c r="F99" s="22" t="n">
         <v>50.455</v>
       </c>
-      <c r="G94" s="22" t="n">
+      <c r="G99" s="22" t="n">
         <v>102.565</v>
       </c>
-      <c r="H94" s="22" t="n">
+      <c r="H99" s="22" t="n">
         <v>55.898</v>
       </c>
-      <c r="I94" s="22" t="n">
+      <c r="I99" s="22" t="n">
         <v>50.365</v>
       </c>
-      <c r="J94" s="22" t="n">
+      <c r="J99" s="22" t="n">
         <v>62.307</v>
       </c>
-      <c r="K94" s="22" t="n">
+      <c r="K99" s="22" t="n">
         <v>138.452</v>
       </c>
-      <c r="L94" s="22" t="n">
+      <c r="L99" s="22" t="n">
         <v>63.187</v>
       </c>
-      <c r="M94" s="22" t="n">
+      <c r="M99" s="22" t="n">
         <v>120.236</v>
       </c>
-      <c r="N94" s="22" t="n">
+      <c r="N99" s="22" t="n">
         <v>137.752</v>
       </c>
-      <c r="U94" s="22" t="n">
+      <c r="U99" s="22" t="n">
         <v>20.611</v>
       </c>
-      <c r="V94" s="22" t="n">
+      <c r="V99" s="22" t="n">
         <v>82.107</v>
       </c>
-      <c r="W94" s="22" t="n">
+      <c r="W99" s="22" t="n">
         <v>50.365</v>
       </c>
-      <c r="X94" s="22" t="n">
+      <c r="X99" s="22" t="n">
         <v>120.236</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="9" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="C95" s="12" t="n">
+      <c r="C100" s="12" t="n">
         <v>103.4</v>
       </c>
-      <c r="D95" s="12" t="n">
+      <c r="D100" s="12" t="n">
         <v>142.051</v>
       </c>
-      <c r="E95" s="12" t="n">
+      <c r="E100" s="12" t="n">
         <v>119.273</v>
       </c>
-      <c r="F95" s="12" t="n">
+      <c r="F100" s="12" t="n">
         <v>113.876</v>
       </c>
-      <c r="G95" s="12" t="n">
+      <c r="G100" s="12" t="n">
         <v>230.262</v>
       </c>
-      <c r="H95" s="12" t="n">
+      <c r="H100" s="12" t="n">
         <v>124.61</v>
       </c>
-      <c r="I95" s="12" t="n">
+      <c r="I100" s="12" t="n">
         <v>68.056</v>
       </c>
-      <c r="J95" s="12" t="n">
+      <c r="J100" s="12" t="n">
         <v>135.746</v>
       </c>
-      <c r="K95" s="12" t="n">
+      <c r="K100" s="12" t="n">
         <v>312.562</v>
       </c>
-      <c r="L95" s="12" t="n">
+      <c r="L100" s="12" t="n">
         <v>141.087</v>
       </c>
-      <c r="M95" s="12" t="n">
+      <c r="M100" s="12" t="n">
         <v>197.17</v>
       </c>
-      <c r="N95" s="12" t="n">
+      <c r="N100" s="12" t="n">
         <v>274.36</v>
       </c>
-      <c r="U95" s="12" t="n">
+      <c r="U100" s="12" t="n">
         <v>56.847</v>
       </c>
-      <c r="V95" s="12" t="n">
+      <c r="V100" s="12" t="n">
         <v>119.273</v>
       </c>
-      <c r="W95" s="12" t="n">
+      <c r="W100" s="12" t="n">
         <v>68.056</v>
       </c>
-      <c r="X95" s="12" t="n">
+      <c r="X100" s="12" t="n">
         <v>197.17</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="18" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G101" s="17">
+        <f>IF(OR(G100="",C100=""),"",IF(C100&lt;=0,"",IFERROR(G100/C100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H101" s="17">
+        <f>IF(OR(H100="",D100=""),"",IF(D100&lt;=0,"",IFERROR(H100/D100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I101" s="17">
+        <f>IF(OR(I100="",E100=""),"",IF(E100&lt;=0,"",IFERROR(I100/E100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J101" s="17">
+        <f>IF(OR(J100="",F100=""),"",IF(F100&lt;=0,"",IFERROR(J100/F100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K101" s="17">
+        <f>IF(OR(K100="",G100=""),"",IF(G100&lt;=0,"",IFERROR(K100/G100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L101" s="17">
+        <f>IF(OR(L100="",H100=""),"",IF(H100&lt;=0,"",IFERROR(L100/H100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M101" s="17">
+        <f>IF(OR(M100="",I100=""),"",IF(I100&lt;=0,"",IFERROR(M100/I100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N101" s="17">
+        <f>IF(OR(N100="",J100=""),"",IF(J100&lt;=0,"",IFERROR(N100/J100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U101" s="17">
+        <f>IF(OR(U100="",T100=""),"",IF(T100&lt;=0,"",IFERROR(U100/T100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V101" s="17">
+        <f>IF(OR(V100="",U100=""),"",IF(U100&lt;=0,"",IFERROR(V100/U100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W101" s="17">
+        <f>IF(OR(W100="",V100=""),"",IF(V100&lt;=0,"",IFERROR(W100/V100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X101" s="17">
+        <f>IF(OR(X100="",W100=""),"",IF(W100&lt;=0,"",IFERROR(X100/W100-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B97" s="44" t="inlineStr">
+      <c r="B103" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C97" s="18" t="n"/>
-      <c r="D97" s="18" t="n"/>
-      <c r="E97" s="18" t="n"/>
-      <c r="F97" s="18" t="n"/>
-      <c r="G97" s="18" t="n"/>
-      <c r="H97" s="18" t="n"/>
-      <c r="I97" s="18" t="n"/>
-      <c r="J97" s="18" t="n"/>
-      <c r="K97" s="18" t="n"/>
-      <c r="L97" s="18" t="n"/>
-      <c r="M97" s="18" t="n"/>
-      <c r="N97" s="18" t="n"/>
-      <c r="O97" s="18" t="n"/>
-      <c r="P97" s="18" t="n"/>
-      <c r="Q97" s="18" t="n"/>
-      <c r="R97" s="18" t="n"/>
-      <c r="S97" s="18" t="n"/>
-      <c r="T97" s="18" t="n"/>
-      <c r="U97" s="18" t="n"/>
-      <c r="V97" s="18" t="n"/>
-      <c r="W97" s="18" t="n"/>
-      <c r="X97" s="18" t="n"/>
-      <c r="Y97" s="18" t="n"/>
-      <c r="Z97" s="18" t="n"/>
-      <c r="AA97" s="18" t="n"/>
-      <c r="AB97" s="18" t="n"/>
-      <c r="AC97" s="18" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="C103" s="18" t="n"/>
+      <c r="D103" s="18" t="n"/>
+      <c r="E103" s="18" t="n"/>
+      <c r="F103" s="18" t="n"/>
+      <c r="G103" s="18" t="n"/>
+      <c r="H103" s="18" t="n"/>
+      <c r="I103" s="18" t="n"/>
+      <c r="J103" s="18" t="n"/>
+      <c r="K103" s="18" t="n"/>
+      <c r="L103" s="18" t="n"/>
+      <c r="M103" s="18" t="n"/>
+      <c r="N103" s="18" t="n"/>
+      <c r="O103" s="18" t="n"/>
+      <c r="P103" s="18" t="n"/>
+      <c r="Q103" s="18" t="n"/>
+      <c r="R103" s="18" t="n"/>
+      <c r="S103" s="18" t="n"/>
+      <c r="T103" s="18" t="n"/>
+      <c r="U103" s="18" t="n"/>
+      <c r="V103" s="18" t="n"/>
+      <c r="W103" s="18" t="n"/>
+      <c r="X103" s="18" t="n"/>
+      <c r="Y103" s="18" t="n"/>
+      <c r="Z103" s="18" t="n"/>
+      <c r="AA103" s="18" t="n"/>
+      <c r="AB103" s="18" t="n"/>
+      <c r="AC103" s="18" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B104" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="E104" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr">
+      <c r="F104" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G98" s="5" t="inlineStr">
+      <c r="G104" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H98" s="5" t="inlineStr">
+      <c r="H104" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I98" s="5" t="inlineStr">
+      <c r="I104" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J98" s="5" t="inlineStr">
+      <c r="J104" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K98" s="5" t="inlineStr">
+      <c r="K104" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L98" s="5" t="inlineStr">
+      <c r="L104" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M98" s="5" t="inlineStr">
+      <c r="M104" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N98" s="5" t="inlineStr">
+      <c r="N104" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O98" s="5" t="inlineStr">
+      <c r="O104" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P98" s="5" t="inlineStr">
+      <c r="P104" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q98" s="5" t="inlineStr">
+      <c r="Q104" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R98" s="5" t="inlineStr">
+      <c r="R104" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S98" s="5" t="inlineStr">
+      <c r="S104" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T98" s="5" t="inlineStr">
+      <c r="T104" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U98" s="5" t="inlineStr">
+      <c r="U104" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V98" s="5" t="inlineStr">
+      <c r="V104" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W98" s="5" t="inlineStr">
+      <c r="W104" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X98" s="5" t="inlineStr">
+      <c r="X104" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y98" s="5" t="inlineStr">
+      <c r="Y104" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z98" s="5" t="inlineStr">
+      <c r="Z104" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA98" s="5" t="inlineStr">
+      <c r="AA104" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB98" s="5" t="inlineStr">
+      <c r="AB104" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC98" s="5" t="inlineStr">
+      <c r="AC104" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="9" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="C99" s="12" t="n">
+      <c r="C105" s="12" t="n">
         <v>246.402</v>
       </c>
-      <c r="E99" s="12" t="n">
+      <c r="E105" s="12" t="n">
         <v>652.499</v>
       </c>
-      <c r="G99" s="12" t="n">
+      <c r="G105" s="12" t="n">
         <v>497.158</v>
       </c>
-      <c r="I99" s="12" t="n">
+      <c r="I105" s="12" t="n">
         <v>796.087</v>
       </c>
-      <c r="K99" s="12" t="n">
+      <c r="K105" s="12" t="n">
         <v>649.068</v>
       </c>
-      <c r="M99" s="12" t="n">
+      <c r="M105" s="12" t="n">
         <v>1170.748</v>
       </c>
-      <c r="T99" s="12" t="n">
+      <c r="T105" s="12" t="n">
         <v>447.639</v>
       </c>
-      <c r="U99" s="12" t="n">
+      <c r="U105" s="12" t="n">
         <v>568.893</v>
       </c>
-      <c r="V99" s="12" t="n">
+      <c r="V105" s="12" t="n">
         <v>652.499</v>
       </c>
-      <c r="W99" s="12" t="n">
+      <c r="W105" s="12" t="n">
         <v>796.087</v>
       </c>
-      <c r="X99" s="12" t="n">
+      <c r="X105" s="12" t="n">
         <v>1170.748</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="20" t="inlineStr">
-        <is>
-          <t>고정자산 제각손실</t>
-        </is>
-      </c>
-      <c r="E100" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V100" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="C101" s="22" t="n">
-        <v>9.122999999999999</v>
-      </c>
-      <c r="E101" s="22" t="n">
-        <v>26.604</v>
-      </c>
-      <c r="G101" s="22" t="n">
-        <v>20.016</v>
-      </c>
-      <c r="I101" s="22" t="n">
-        <v>55.047</v>
-      </c>
-      <c r="K101" s="22" t="n">
-        <v>40.285</v>
-      </c>
-      <c r="M101" s="22" t="n">
-        <v>84.108</v>
-      </c>
-      <c r="T101" s="22" t="n">
-        <v>30.195</v>
-      </c>
-      <c r="U101" s="22" t="n">
-        <v>28.323</v>
-      </c>
-      <c r="V101" s="22" t="n">
-        <v>26.604</v>
-      </c>
-      <c r="W101" s="22" t="n">
-        <v>55.047</v>
-      </c>
-      <c r="X101" s="22" t="n">
-        <v>84.108</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="20" t="inlineStr">
-        <is>
-          <t>보증금 상각비</t>
-        </is>
-      </c>
-      <c r="C102" s="22" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E102" s="22" t="n">
-        <v>5.963</v>
-      </c>
-      <c r="G102" s="22" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="I102" s="22" t="n">
-        <v>1.305</v>
-      </c>
-      <c r="K102" s="22" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="M102" s="22" t="n">
-        <v>1.305</v>
-      </c>
-      <c r="T102" s="22" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="U102" s="22" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="V102" s="22" t="n">
-        <v>5.963</v>
-      </c>
-      <c r="W102" s="22" t="n">
-        <v>1.305</v>
-      </c>
-      <c r="X102" s="22" t="n">
-        <v>1.305</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="20" t="inlineStr">
-        <is>
-          <t>임원 퇴직위로 충당금 증감</t>
-        </is>
-      </c>
-      <c r="E103" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" s="22" t="n">
-        <v>28.106</v>
-      </c>
-      <c r="U103" s="22" t="n">
-        <v>-225.931</v>
-      </c>
-      <c r="V103" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="20" t="inlineStr">
-        <is>
-          <t>장기미지급금 증감</t>
-        </is>
-      </c>
-      <c r="E104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" s="22" t="n">
-        <v>225.931</v>
-      </c>
-      <c r="V104" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="20" t="inlineStr">
-        <is>
-          <t>주식보상비용</t>
-        </is>
-      </c>
-      <c r="C105" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="22" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="I105" s="22" t="n">
-        <v>3.398</v>
-      </c>
-      <c r="K105" s="22" t="n">
-        <v>2.912</v>
-      </c>
-      <c r="M105" s="22" t="n">
-        <v>6.182</v>
-      </c>
-      <c r="V105" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W105" s="22" t="n">
-        <v>3.398</v>
-      </c>
-      <c r="X105" s="22" t="n">
-        <v>6.182</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="20" t="inlineStr">
         <is>
-          <t>충당금 증감</t>
-        </is>
-      </c>
-      <c r="C106" s="22" t="n">
-        <v>9.053000000000001</v>
-      </c>
-      <c r="G106" s="22" t="n">
-        <v>10.191</v>
-      </c>
-      <c r="K106" s="22" t="n">
-        <v>29.882</v>
+          <t>고정자산 제각손실</t>
+        </is>
+      </c>
+      <c r="E106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="C107" s="22" t="n">
-        <v>-0.008999999999999999</v>
+        <v>9.122999999999999</v>
+      </c>
+      <c r="E107" s="22" t="n">
+        <v>26.604</v>
       </c>
       <c r="G107" s="22" t="n">
-        <v>-3.698</v>
+        <v>20.016</v>
+      </c>
+      <c r="I107" s="22" t="n">
+        <v>55.047</v>
       </c>
       <c r="K107" s="22" t="n">
-        <v>-8.205</v>
+        <v>40.285</v>
+      </c>
+      <c r="M107" s="22" t="n">
+        <v>84.108</v>
+      </c>
+      <c r="T107" s="22" t="n">
+        <v>30.195</v>
+      </c>
+      <c r="U107" s="22" t="n">
+        <v>28.323</v>
+      </c>
+      <c r="V107" s="22" t="n">
+        <v>26.604</v>
+      </c>
+      <c r="W107" s="22" t="n">
+        <v>55.047</v>
+      </c>
+      <c r="X107" s="22" t="n">
+        <v>84.108</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
-        </is>
+          <t>보증금 상각비</t>
+        </is>
+      </c>
+      <c r="C108" s="22" t="n">
+        <v>0.18</v>
       </c>
       <c r="E108" s="22" t="n">
-        <v>-0.025</v>
+        <v>5.963</v>
+      </c>
+      <c r="G108" s="22" t="n">
+        <v>0.652</v>
       </c>
       <c r="I108" s="22" t="n">
-        <v>-18.243</v>
+        <v>1.305</v>
+      </c>
+      <c r="K108" s="22" t="n">
+        <v>0.652</v>
       </c>
       <c r="M108" s="22" t="n">
-        <v>-11.335</v>
+        <v>1.305</v>
       </c>
       <c r="T108" s="22" t="n">
-        <v>-0.025</v>
+        <v>0.36</v>
       </c>
       <c r="U108" s="22" t="n">
-        <v>-0.013</v>
+        <v>0.36</v>
       </c>
       <c r="V108" s="22" t="n">
-        <v>-0.025</v>
+        <v>5.963</v>
       </c>
       <c r="W108" s="22" t="n">
-        <v>-18.243</v>
+        <v>1.305</v>
       </c>
       <c r="X108" s="22" t="n">
-        <v>-11.335</v>
+        <v>1.305</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="20" t="inlineStr">
         <is>
-          <t>외환차손익</t>
-        </is>
-      </c>
-      <c r="C109" s="22" t="n">
-        <v>-12.24</v>
+          <t>임원 퇴직위로 충당금 증감</t>
+        </is>
       </c>
       <c r="E109" s="22" t="n">
-        <v>-27.755</v>
-      </c>
-      <c r="G109" s="22" t="n">
-        <v>12.308</v>
-      </c>
-      <c r="I109" s="22" t="n">
-        <v>62.808</v>
-      </c>
-      <c r="K109" s="22" t="n">
-        <v>-29.503</v>
-      </c>
-      <c r="M109" s="22" t="n">
-        <v>-39.882</v>
+        <v>0</v>
       </c>
       <c r="T109" s="22" t="n">
-        <v>-11.913</v>
+        <v>28.106</v>
       </c>
       <c r="U109" s="22" t="n">
-        <v>-8.737</v>
+        <v>-225.931</v>
       </c>
       <c r="V109" s="22" t="n">
-        <v>-27.755</v>
-      </c>
-      <c r="W109" s="22" t="n">
-        <v>62.808</v>
-      </c>
-      <c r="X109" s="22" t="n">
-        <v>-39.882</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
-        </is>
-      </c>
-      <c r="C110" s="22" t="n">
-        <v>-255.678</v>
+          <t>장기미지급금 증감</t>
+        </is>
       </c>
       <c r="E110" s="22" t="n">
-        <v>-284.202</v>
-      </c>
-      <c r="G110" s="22" t="n">
-        <v>-209.296</v>
-      </c>
-      <c r="I110" s="22" t="n">
-        <v>275.134</v>
-      </c>
-      <c r="K110" s="22" t="n">
-        <v>-352.642</v>
-      </c>
-      <c r="M110" s="22" t="n">
-        <v>-110.596</v>
+        <v>0</v>
       </c>
       <c r="T110" s="22" t="n">
-        <v>323.398</v>
+        <v>0</v>
       </c>
       <c r="U110" s="22" t="n">
-        <v>29.007</v>
+        <v>225.931</v>
       </c>
       <c r="V110" s="22" t="n">
-        <v>-284.202</v>
-      </c>
-      <c r="W110" s="22" t="n">
-        <v>275.134</v>
-      </c>
-      <c r="X110" s="22" t="n">
-        <v>-110.596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
+          <t>주식보상비용</t>
         </is>
       </c>
       <c r="C111" s="22" t="n">
-        <v>47.78</v>
+        <v>0</v>
       </c>
       <c r="E111" s="22" t="n">
-        <v>-155.997</v>
+        <v>0</v>
       </c>
       <c r="G111" s="22" t="n">
-        <v>-27.949</v>
+        <v>0.485</v>
       </c>
       <c r="I111" s="22" t="n">
-        <v>-123.404</v>
+        <v>3.398</v>
       </c>
       <c r="K111" s="22" t="n">
-        <v>-300</v>
+        <v>2.912</v>
       </c>
       <c r="M111" s="22" t="n">
-        <v>-1064.594</v>
-      </c>
-      <c r="T111" s="22" t="n">
-        <v>-309.138</v>
-      </c>
-      <c r="U111" s="22" t="n">
-        <v>-97.667</v>
+        <v>6.182</v>
       </c>
       <c r="V111" s="22" t="n">
-        <v>-155.997</v>
+        <v>0</v>
       </c>
       <c r="W111" s="22" t="n">
-        <v>-123.404</v>
+        <v>3.398</v>
       </c>
       <c r="X111" s="22" t="n">
-        <v>-1064.594</v>
+        <v>6.182</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
+          <t>충당금 증감</t>
         </is>
       </c>
       <c r="C112" s="22" t="n">
-        <v>174.022</v>
-      </c>
-      <c r="E112" s="22" t="n">
-        <v>218.718</v>
+        <v>9.053000000000001</v>
       </c>
       <c r="G112" s="22" t="n">
-        <v>-189.415</v>
-      </c>
-      <c r="I112" s="22" t="n">
-        <v>-98.407</v>
+        <v>10.191</v>
       </c>
       <c r="K112" s="22" t="n">
-        <v>219.949</v>
-      </c>
-      <c r="M112" s="22" t="n">
-        <v>194.634</v>
-      </c>
-      <c r="T112" s="22" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="U112" s="22" t="n">
-        <v>70.104</v>
-      </c>
-      <c r="V112" s="22" t="n">
-        <v>218.718</v>
-      </c>
-      <c r="W112" s="22" t="n">
-        <v>-98.407</v>
-      </c>
-      <c r="X112" s="22" t="n">
-        <v>194.634</v>
+        <v>29.882</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="20" t="inlineStr">
         <is>
-          <t>기타 자산 증감</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="C113" s="22" t="n">
-        <v>-25.919</v>
-      </c>
-      <c r="E113" s="22" t="n">
-        <v>-1.171</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="G113" s="22" t="n">
-        <v>-123.134</v>
-      </c>
-      <c r="I113" s="22" t="n">
-        <v>-0.193</v>
+        <v>-3.698</v>
       </c>
       <c r="K113" s="22" t="n">
-        <v>-17.343</v>
-      </c>
-      <c r="M113" s="22" t="n">
-        <v>-1607.896</v>
-      </c>
-      <c r="T113" s="22" t="n">
-        <v>1.385</v>
-      </c>
-      <c r="U113" s="22" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="V113" s="22" t="n">
-        <v>-1.171</v>
-      </c>
-      <c r="W113" s="22" t="n">
-        <v>-0.193</v>
-      </c>
-      <c r="X113" s="22" t="n">
-        <v>-1607.896</v>
+        <v>-8.205</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="20" t="inlineStr">
         <is>
-          <t>기타 부채 증감</t>
-        </is>
-      </c>
-      <c r="C114" s="22" t="n">
-        <v>62.128</v>
+          <t>이자·배당금 수익</t>
+        </is>
       </c>
       <c r="E114" s="22" t="n">
-        <v>540.223</v>
-      </c>
-      <c r="G114" s="22" t="n">
-        <v>9.359999999999999</v>
+        <v>-0.025</v>
       </c>
       <c r="I114" s="22" t="n">
-        <v>-188.353</v>
-      </c>
-      <c r="K114" s="22" t="n">
-        <v>180.874</v>
+        <v>-18.243</v>
       </c>
       <c r="M114" s="22" t="n">
-        <v>247.475</v>
+        <v>-11.335</v>
       </c>
       <c r="T114" s="22" t="n">
-        <v>199.811</v>
+        <v>-0.025</v>
       </c>
       <c r="U114" s="22" t="n">
-        <v>159.265</v>
+        <v>-0.013</v>
       </c>
       <c r="V114" s="22" t="n">
-        <v>540.223</v>
+        <v>-0.025</v>
       </c>
       <c r="W114" s="22" t="n">
-        <v>-188.353</v>
+        <v>-18.243</v>
       </c>
       <c r="X114" s="22" t="n">
-        <v>247.475</v>
+        <v>-11.335</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>외환차손익</t>
         </is>
       </c>
       <c r="C115" s="22" t="n">
-        <v>254.844</v>
+        <v>-12.24</v>
       </c>
       <c r="E115" s="22" t="n">
-        <v>974.857</v>
+        <v>-27.755</v>
       </c>
       <c r="G115" s="22" t="n">
-        <v>-3.321</v>
+        <v>12.308</v>
       </c>
       <c r="I115" s="22" t="n">
-        <v>765.178</v>
+        <v>62.808</v>
       </c>
       <c r="K115" s="22" t="n">
-        <v>415.929</v>
+        <v>-29.503</v>
       </c>
       <c r="M115" s="22" t="n">
-        <v>-1129.849</v>
+        <v>-39.882</v>
       </c>
       <c r="T115" s="22" t="n">
-        <v>710.665</v>
+        <v>-11.913</v>
       </c>
       <c r="U115" s="22" t="n">
-        <v>749.755</v>
+        <v>-8.737</v>
       </c>
       <c r="V115" s="22" t="n">
-        <v>974.857</v>
+        <v>-27.755</v>
       </c>
       <c r="W115" s="22" t="n">
-        <v>765.178</v>
+        <v>62.808</v>
       </c>
       <c r="X115" s="22" t="n">
-        <v>-1129.849</v>
+        <v>-39.882</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="20" t="inlineStr">
         <is>
-          <t>이자 수취</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="C116" s="22" t="n">
-        <v>0.008999999999999999</v>
+        <v>-255.678</v>
+      </c>
+      <c r="E116" s="22" t="n">
+        <v>-284.202</v>
       </c>
       <c r="G116" s="22" t="n">
-        <v>2.927</v>
+        <v>-209.296</v>
+      </c>
+      <c r="I116" s="22" t="n">
+        <v>275.134</v>
       </c>
       <c r="K116" s="22" t="n">
-        <v>9.795</v>
+        <v>-352.642</v>
+      </c>
+      <c r="M116" s="22" t="n">
+        <v>-110.596</v>
+      </c>
+      <c r="T116" s="22" t="n">
+        <v>323.398</v>
+      </c>
+      <c r="U116" s="22" t="n">
+        <v>29.007</v>
+      </c>
+      <c r="V116" s="22" t="n">
+        <v>-284.202</v>
+      </c>
+      <c r="W116" s="22" t="n">
+        <v>275.134</v>
+      </c>
+      <c r="X116" s="22" t="n">
+        <v>-110.596</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
-        </is>
+          <t>재고자산 증감</t>
+        </is>
+      </c>
+      <c r="C117" s="22" t="n">
+        <v>47.78</v>
       </c>
       <c r="E117" s="22" t="n">
-        <v>0.025</v>
+        <v>-155.997</v>
+      </c>
+      <c r="G117" s="22" t="n">
+        <v>-27.949</v>
       </c>
       <c r="I117" s="22" t="n">
-        <v>16.652</v>
+        <v>-123.404</v>
+      </c>
+      <c r="K117" s="22" t="n">
+        <v>-300</v>
       </c>
       <c r="M117" s="22" t="n">
-        <v>12.925</v>
+        <v>-1064.594</v>
       </c>
       <c r="T117" s="22" t="n">
-        <v>0.025</v>
+        <v>-309.138</v>
       </c>
       <c r="U117" s="22" t="n">
-        <v>0.013</v>
+        <v>-97.667</v>
       </c>
       <c r="V117" s="22" t="n">
-        <v>0.025</v>
+        <v>-155.997</v>
       </c>
       <c r="W117" s="22" t="n">
-        <v>16.652</v>
+        <v>-123.404</v>
       </c>
       <c r="X117" s="22" t="n">
-        <v>12.925</v>
+        <v>-1064.594</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="C118" s="22" t="n">
-        <v>-116.945</v>
+        <v>174.022</v>
       </c>
       <c r="E118" s="22" t="n">
-        <v>-217.311</v>
+        <v>218.718</v>
       </c>
       <c r="G118" s="22" t="n">
-        <v>-88.949</v>
+        <v>-189.415</v>
       </c>
       <c r="I118" s="22" t="n">
-        <v>-185.494</v>
+        <v>-98.407</v>
       </c>
       <c r="K118" s="22" t="n">
-        <v>-184.947</v>
+        <v>219.949</v>
       </c>
       <c r="M118" s="22" t="n">
-        <v>-332.659</v>
+        <v>194.634</v>
       </c>
       <c r="T118" s="22" t="n">
-        <v>-245.108</v>
+        <v>0.844</v>
       </c>
       <c r="U118" s="22" t="n">
-        <v>-168.104</v>
+        <v>70.104</v>
       </c>
       <c r="V118" s="22" t="n">
-        <v>-217.311</v>
+        <v>218.718</v>
       </c>
       <c r="W118" s="22" t="n">
-        <v>-185.494</v>
+        <v>-98.407</v>
       </c>
       <c r="X118" s="22" t="n">
-        <v>-332.659</v>
+        <v>194.634</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C119" s="12" t="n">
-        <v>137.908</v>
-      </c>
-      <c r="E119" s="12" t="n">
-        <v>757.572</v>
-      </c>
-      <c r="G119" s="12" t="n">
-        <v>-89.343</v>
-      </c>
-      <c r="I119" s="12" t="n">
-        <v>596.336</v>
-      </c>
-      <c r="K119" s="12" t="n">
-        <v>240.777</v>
-      </c>
-      <c r="M119" s="12" t="n">
-        <v>-1449.582</v>
-      </c>
-      <c r="T119" s="12" t="n">
-        <v>465.582</v>
-      </c>
-      <c r="U119" s="12" t="n">
-        <v>581.665</v>
-      </c>
-      <c r="V119" s="12" t="n">
-        <v>757.572</v>
-      </c>
-      <c r="W119" s="12" t="n">
-        <v>596.336</v>
-      </c>
-      <c r="X119" s="12" t="n">
-        <v>-1449.582</v>
+      <c r="A119" s="20" t="inlineStr">
+        <is>
+          <t>기타 자산 증감</t>
+        </is>
+      </c>
+      <c r="C119" s="22" t="n">
+        <v>-25.919</v>
+      </c>
+      <c r="E119" s="22" t="n">
+        <v>-1.171</v>
+      </c>
+      <c r="G119" s="22" t="n">
+        <v>-123.134</v>
+      </c>
+      <c r="I119" s="22" t="n">
+        <v>-0.193</v>
+      </c>
+      <c r="K119" s="22" t="n">
+        <v>-17.343</v>
+      </c>
+      <c r="M119" s="22" t="n">
+        <v>-1607.896</v>
+      </c>
+      <c r="T119" s="22" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="U119" s="22" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="V119" s="22" t="n">
+        <v>-1.171</v>
+      </c>
+      <c r="W119" s="22" t="n">
+        <v>-0.193</v>
+      </c>
+      <c r="X119" s="22" t="n">
+        <v>-1607.896</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>기타 부채 증감</t>
         </is>
       </c>
       <c r="C120" s="22" t="n">
-        <v>-3.289</v>
+        <v>62.128</v>
       </c>
       <c r="E120" s="22" t="n">
-        <v>-75.14400000000001</v>
+        <v>540.223</v>
       </c>
       <c r="G120" s="22" t="n">
-        <v>-7.835</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="I120" s="22" t="n">
-        <v>-100.922</v>
+        <v>-188.353</v>
       </c>
       <c r="K120" s="22" t="n">
-        <v>-12.695</v>
+        <v>180.874</v>
       </c>
       <c r="M120" s="22" t="n">
-        <v>-20.733</v>
+        <v>247.475</v>
       </c>
       <c r="T120" s="22" t="n">
-        <v>-7.816</v>
+        <v>199.811</v>
       </c>
       <c r="U120" s="22" t="n">
-        <v>-6.16</v>
+        <v>159.265</v>
       </c>
       <c r="V120" s="22" t="n">
-        <v>-75.14400000000001</v>
+        <v>540.223</v>
       </c>
       <c r="W120" s="22" t="n">
-        <v>-100.922</v>
+        <v>-188.353</v>
       </c>
       <c r="X120" s="22" t="n">
-        <v>-20.733</v>
+        <v>247.475</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>소계</t>
         </is>
       </c>
       <c r="C121" s="22" t="n">
-        <v>0</v>
+        <v>254.844</v>
       </c>
       <c r="E121" s="22" t="n">
-        <v>0</v>
+        <v>974.857</v>
       </c>
       <c r="G121" s="22" t="n">
-        <v>-15.095</v>
+        <v>-3.321</v>
       </c>
       <c r="I121" s="22" t="n">
-        <v>-23.795</v>
+        <v>765.178</v>
       </c>
       <c r="K121" s="22" t="n">
-        <v>-14.85</v>
+        <v>415.929</v>
       </c>
       <c r="M121" s="22" t="n">
-        <v>-19.55</v>
+        <v>-1129.849</v>
+      </c>
+      <c r="T121" s="22" t="n">
+        <v>710.665</v>
+      </c>
+      <c r="U121" s="22" t="n">
+        <v>749.755</v>
       </c>
       <c r="V121" s="22" t="n">
-        <v>0</v>
+        <v>974.857</v>
       </c>
       <c r="W121" s="22" t="n">
-        <v>-23.795</v>
+        <v>765.178</v>
       </c>
       <c r="X121" s="22" t="n">
-        <v>-19.55</v>
+        <v>-1129.849</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="20" t="inlineStr">
         <is>
-          <t>임차보증금 납입</t>
+          <t>이자 수취</t>
         </is>
       </c>
       <c r="C122" s="22" t="n">
-        <v>-21.232</v>
-      </c>
-      <c r="E122" s="22" t="n">
-        <v>-21.379</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G122" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" s="22" t="n">
-        <v>-1.468</v>
-      </c>
-      <c r="M122" s="22" t="n">
-        <v>-3.212</v>
-      </c>
-      <c r="T122" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" s="22" t="n">
-        <v>-0.8139999999999999</v>
-      </c>
-      <c r="V122" s="22" t="n">
-        <v>-21.379</v>
-      </c>
-      <c r="W122" s="22" t="n">
-        <v>-1.468</v>
-      </c>
-      <c r="X122" s="22" t="n">
-        <v>-3.212</v>
+        <v>2.927</v>
+      </c>
+      <c r="K122" s="22" t="n">
+        <v>9.795</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="20" t="inlineStr">
         <is>
-          <t>임차보증금 회수</t>
-        </is>
+          <t>이자·배당금 수취</t>
+        </is>
+      </c>
+      <c r="E123" s="22" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I123" s="22" t="n">
+        <v>16.652</v>
+      </c>
+      <c r="M123" s="22" t="n">
+        <v>12.925</v>
       </c>
       <c r="T123" s="22" t="n">
-        <v>0.082</v>
+        <v>0.025</v>
       </c>
       <c r="U123" s="22" t="n">
-        <v>0</v>
+        <v>0.013</v>
+      </c>
+      <c r="V123" s="22" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="W123" s="22" t="n">
+        <v>16.652</v>
+      </c>
+      <c r="X123" s="22" t="n">
+        <v>12.925</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20" t="inlineStr">
         <is>
-          <t>임차보증금·보증금 회수</t>
-        </is>
+          <t>법인세 납부</t>
+        </is>
+      </c>
+      <c r="C124" s="22" t="n">
+        <v>-116.945</v>
       </c>
       <c r="E124" s="22" t="n">
-        <v>9.863</v>
+        <v>-217.311</v>
+      </c>
+      <c r="G124" s="22" t="n">
+        <v>-88.949</v>
       </c>
       <c r="I124" s="22" t="n">
-        <v>0</v>
+        <v>-185.494</v>
+      </c>
+      <c r="K124" s="22" t="n">
+        <v>-184.947</v>
+      </c>
+      <c r="M124" s="22" t="n">
+        <v>-332.659</v>
+      </c>
+      <c r="T124" s="22" t="n">
+        <v>-245.108</v>
       </c>
       <c r="U124" s="22" t="n">
-        <v>0</v>
+        <v>-168.104</v>
       </c>
       <c r="V124" s="22" t="n">
-        <v>9.863</v>
+        <v>-217.311</v>
       </c>
       <c r="W124" s="22" t="n">
-        <v>0</v>
+        <v>-185.494</v>
+      </c>
+      <c r="X124" s="22" t="n">
+        <v>-332.659</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="20" t="inlineStr">
-        <is>
-          <t>자산복구부채 이행 지출</t>
-        </is>
-      </c>
-      <c r="E125" s="22" t="n">
-        <v>-6.15</v>
-      </c>
-      <c r="I125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V125" s="22" t="n">
-        <v>-6.15</v>
-      </c>
-      <c r="W125" s="22" t="n">
-        <v>0</v>
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="n">
+        <v>137.908</v>
+      </c>
+      <c r="E125" s="12" t="n">
+        <v>757.572</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>-89.343</v>
+      </c>
+      <c r="I125" s="12" t="n">
+        <v>596.336</v>
+      </c>
+      <c r="K125" s="12" t="n">
+        <v>240.777</v>
+      </c>
+      <c r="M125" s="12" t="n">
+        <v>-1449.582</v>
+      </c>
+      <c r="T125" s="12" t="n">
+        <v>465.582</v>
+      </c>
+      <c r="U125" s="12" t="n">
+        <v>581.665</v>
+      </c>
+      <c r="V125" s="12" t="n">
+        <v>757.572</v>
+      </c>
+      <c r="W125" s="12" t="n">
+        <v>596.336</v>
+      </c>
+      <c r="X125" s="12" t="n">
+        <v>-1449.582</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="20" t="inlineStr">
         <is>
-          <t>장기선급비용 지출</t>
-        </is>
+          <t>유형자산 취득(설비투자)</t>
+        </is>
+      </c>
+      <c r="C126" s="22" t="n">
+        <v>-3.289</v>
       </c>
       <c r="E126" s="22" t="n">
-        <v>-1.683</v>
+        <v>-75.14400000000001</v>
+      </c>
+      <c r="G126" s="22" t="n">
+        <v>-7.835</v>
       </c>
       <c r="I126" s="22" t="n">
-        <v>0</v>
+        <v>-100.922</v>
+      </c>
+      <c r="K126" s="22" t="n">
+        <v>-12.695</v>
+      </c>
+      <c r="M126" s="22" t="n">
+        <v>-20.733</v>
+      </c>
+      <c r="T126" s="22" t="n">
+        <v>-7.816</v>
       </c>
       <c r="U126" s="22" t="n">
-        <v>0</v>
+        <v>-6.16</v>
       </c>
       <c r="V126" s="22" t="n">
-        <v>-1.683</v>
+        <v>-75.14400000000001</v>
       </c>
       <c r="W126" s="22" t="n">
-        <v>0</v>
+        <v>-100.922</v>
+      </c>
+      <c r="X126" s="22" t="n">
+        <v>-20.733</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
-          <t>기타 지출</t>
+          <t>무형자산 취득</t>
         </is>
       </c>
       <c r="C127" s="22" t="n">
@@ -7589,298 +7818,448 @@
         <v>0</v>
       </c>
       <c r="G127" s="22" t="n">
-        <v>-0.703</v>
+        <v>-15.095</v>
       </c>
       <c r="I127" s="22" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-23.795</v>
       </c>
       <c r="K127" s="22" t="n">
-        <v>0</v>
+        <v>-14.85</v>
       </c>
       <c r="M127" s="22" t="n">
-        <v>0</v>
+        <v>-19.55</v>
       </c>
       <c r="V127" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W127" s="22" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-23.795</v>
       </c>
       <c r="X127" s="22" t="n">
+        <v>-19.55</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="20" t="inlineStr">
+        <is>
+          <t>임차보증금 납입</t>
+        </is>
+      </c>
+      <c r="C128" s="22" t="n">
+        <v>-21.232</v>
+      </c>
+      <c r="E128" s="22" t="n">
+        <v>-21.379</v>
+      </c>
+      <c r="G128" s="22" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C128" s="12" t="n">
-        <v>-24.521</v>
-      </c>
-      <c r="E128" s="12" t="n">
-        <v>-94.49299999999999</v>
-      </c>
-      <c r="G128" s="12" t="n">
-        <v>-23.634</v>
-      </c>
-      <c r="I128" s="12" t="n">
-        <v>-126.872</v>
-      </c>
-      <c r="K128" s="12" t="n">
-        <v>-27.545</v>
-      </c>
-      <c r="M128" s="12" t="n">
-        <v>-43.496</v>
-      </c>
-      <c r="T128" s="12" t="n">
-        <v>-7.734</v>
-      </c>
-      <c r="U128" s="12" t="n">
-        <v>-6.974</v>
-      </c>
-      <c r="V128" s="12" t="n">
-        <v>-94.49299999999999</v>
-      </c>
-      <c r="W128" s="12" t="n">
-        <v>-126.872</v>
-      </c>
-      <c r="X128" s="12" t="n">
-        <v>-43.496</v>
+      <c r="I128" s="22" t="n">
+        <v>-1.468</v>
+      </c>
+      <c r="M128" s="22" t="n">
+        <v>-3.212</v>
+      </c>
+      <c r="T128" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" s="22" t="n">
+        <v>-0.8139999999999999</v>
+      </c>
+      <c r="V128" s="22" t="n">
+        <v>-21.379</v>
+      </c>
+      <c r="W128" s="22" t="n">
+        <v>-1.468</v>
+      </c>
+      <c r="X128" s="22" t="n">
+        <v>-3.212</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>주식 발행</t>
-        </is>
-      </c>
-      <c r="C129" s="22" t="n">
-        <v>502.601</v>
-      </c>
-      <c r="E129" s="22" t="n">
-        <v>510.25</v>
-      </c>
-      <c r="G129" s="22" t="n">
-        <v>0.671</v>
-      </c>
-      <c r="I129" s="22" t="n">
-        <v>11.509</v>
-      </c>
-      <c r="K129" s="22" t="n">
-        <v>6.537</v>
-      </c>
-      <c r="M129" s="22" t="n">
-        <v>15.676</v>
+          <t>임차보증금 회수</t>
+        </is>
+      </c>
+      <c r="T129" s="22" t="n">
+        <v>0.082</v>
       </c>
       <c r="U129" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="V129" s="22" t="n">
-        <v>510.25</v>
-      </c>
-      <c r="W129" s="22" t="n">
-        <v>11.509</v>
-      </c>
-      <c r="X129" s="22" t="n">
-        <v>15.676</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
-        </is>
-      </c>
-      <c r="C130" s="22" t="n">
-        <v>-0.27</v>
+          <t>임차보증금·보증금 회수</t>
+        </is>
       </c>
       <c r="E130" s="22" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="G130" s="22" t="n">
-        <v>-0.672</v>
+        <v>9.863</v>
       </c>
       <c r="I130" s="22" t="n">
-        <v>-0.717</v>
-      </c>
-      <c r="K130" s="22" t="n">
-        <v>-0.099</v>
-      </c>
-      <c r="M130" s="22" t="n">
-        <v>-0.255</v>
+        <v>0</v>
       </c>
       <c r="U130" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V130" s="22" t="n">
-        <v>-0.27</v>
+        <v>9.863</v>
       </c>
       <c r="W130" s="22" t="n">
-        <v>-0.717</v>
-      </c>
-      <c r="X130" s="22" t="n">
-        <v>-0.255</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
-        </is>
-      </c>
-      <c r="C131" s="22" t="n">
-        <v>-74.40000000000001</v>
+          <t>자산복구부채 이행 지출</t>
+        </is>
       </c>
       <c r="E131" s="22" t="n">
-        <v>-74.40000000000001</v>
-      </c>
-      <c r="G131" s="22" t="n">
-        <v>-89.447</v>
+        <v>-6.15</v>
       </c>
       <c r="I131" s="22" t="n">
-        <v>-89.464</v>
-      </c>
-      <c r="K131" s="22" t="n">
-        <v>-124.261</v>
-      </c>
-      <c r="M131" s="22" t="n">
-        <v>-124.392</v>
-      </c>
-      <c r="T131" s="22" t="n">
-        <v>-46.608</v>
+        <v>0</v>
       </c>
       <c r="U131" s="22" t="n">
-        <v>-56.634</v>
+        <v>0</v>
       </c>
       <c r="V131" s="22" t="n">
-        <v>-74.40000000000001</v>
+        <v>-6.15</v>
       </c>
       <c r="W131" s="22" t="n">
-        <v>-89.464</v>
-      </c>
-      <c r="X131" s="22" t="n">
-        <v>-124.392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C132" s="12" t="n">
-        <v>427.931</v>
-      </c>
-      <c r="E132" s="12" t="n">
-        <v>435.58</v>
-      </c>
-      <c r="G132" s="12" t="n">
-        <v>-89.449</v>
-      </c>
-      <c r="I132" s="12" t="n">
-        <v>-78.67100000000001</v>
-      </c>
-      <c r="K132" s="12" t="n">
-        <v>-117.823</v>
-      </c>
-      <c r="M132" s="12" t="n">
-        <v>-108.971</v>
-      </c>
-      <c r="T132" s="12" t="n">
-        <v>-46.608</v>
-      </c>
-      <c r="U132" s="12" t="n">
-        <v>-56.634</v>
-      </c>
-      <c r="V132" s="12" t="n">
-        <v>435.58</v>
-      </c>
-      <c r="W132" s="12" t="n">
-        <v>-78.67100000000001</v>
-      </c>
-      <c r="X132" s="12" t="n">
-        <v>-108.971</v>
+      <c r="A132" s="20" t="inlineStr">
+        <is>
+          <t>장기선급비용 지출</t>
+        </is>
+      </c>
+      <c r="E132" s="22" t="n">
+        <v>-1.683</v>
+      </c>
+      <c r="I132" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" s="22" t="n">
+        <v>-1.683</v>
+      </c>
+      <c r="W132" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
+          <t>기타 지출</t>
+        </is>
+      </c>
+      <c r="C133" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" s="22" t="n">
+        <v>-0.703</v>
+      </c>
+      <c r="I133" s="22" t="n">
+        <v>-0.6860000000000001</v>
+      </c>
+      <c r="K133" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" s="22" t="n">
+        <v>-0.6860000000000001</v>
+      </c>
+      <c r="X133" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C134" s="12" t="n">
+        <v>-24.521</v>
+      </c>
+      <c r="E134" s="12" t="n">
+        <v>-94.49299999999999</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>-23.634</v>
+      </c>
+      <c r="I134" s="12" t="n">
+        <v>-126.872</v>
+      </c>
+      <c r="K134" s="12" t="n">
+        <v>-27.545</v>
+      </c>
+      <c r="M134" s="12" t="n">
+        <v>-43.496</v>
+      </c>
+      <c r="T134" s="12" t="n">
+        <v>-7.734</v>
+      </c>
+      <c r="U134" s="12" t="n">
+        <v>-6.974</v>
+      </c>
+      <c r="V134" s="12" t="n">
+        <v>-94.49299999999999</v>
+      </c>
+      <c r="W134" s="12" t="n">
+        <v>-126.872</v>
+      </c>
+      <c r="X134" s="12" t="n">
+        <v>-43.496</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="20" t="inlineStr">
+        <is>
+          <t>주식 발행</t>
+        </is>
+      </c>
+      <c r="C135" s="22" t="n">
+        <v>502.601</v>
+      </c>
+      <c r="E135" s="22" t="n">
+        <v>510.25</v>
+      </c>
+      <c r="G135" s="22" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="I135" s="22" t="n">
+        <v>11.509</v>
+      </c>
+      <c r="K135" s="22" t="n">
+        <v>6.537</v>
+      </c>
+      <c r="M135" s="22" t="n">
+        <v>15.676</v>
+      </c>
+      <c r="U135" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" s="22" t="n">
+        <v>510.25</v>
+      </c>
+      <c r="W135" s="22" t="n">
+        <v>11.509</v>
+      </c>
+      <c r="X135" s="22" t="n">
+        <v>15.676</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="C136" s="22" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="E136" s="22" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="G136" s="22" t="n">
+        <v>-0.672</v>
+      </c>
+      <c r="I136" s="22" t="n">
+        <v>-0.717</v>
+      </c>
+      <c r="K136" s="22" t="n">
+        <v>-0.099</v>
+      </c>
+      <c r="M136" s="22" t="n">
+        <v>-0.255</v>
+      </c>
+      <c r="U136" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" s="22" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="W136" s="22" t="n">
+        <v>-0.717</v>
+      </c>
+      <c r="X136" s="22" t="n">
+        <v>-0.255</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="C137" s="22" t="n">
+        <v>-74.40000000000001</v>
+      </c>
+      <c r="E137" s="22" t="n">
+        <v>-74.40000000000001</v>
+      </c>
+      <c r="G137" s="22" t="n">
+        <v>-89.447</v>
+      </c>
+      <c r="I137" s="22" t="n">
+        <v>-89.464</v>
+      </c>
+      <c r="K137" s="22" t="n">
+        <v>-124.261</v>
+      </c>
+      <c r="M137" s="22" t="n">
+        <v>-124.392</v>
+      </c>
+      <c r="T137" s="22" t="n">
+        <v>-46.608</v>
+      </c>
+      <c r="U137" s="22" t="n">
+        <v>-56.634</v>
+      </c>
+      <c r="V137" s="22" t="n">
+        <v>-74.40000000000001</v>
+      </c>
+      <c r="W137" s="22" t="n">
+        <v>-89.464</v>
+      </c>
+      <c r="X137" s="22" t="n">
+        <v>-124.392</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C138" s="12" t="n">
+        <v>427.931</v>
+      </c>
+      <c r="E138" s="12" t="n">
+        <v>435.58</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>-89.449</v>
+      </c>
+      <c r="I138" s="12" t="n">
+        <v>-78.67100000000001</v>
+      </c>
+      <c r="K138" s="12" t="n">
+        <v>-117.823</v>
+      </c>
+      <c r="M138" s="12" t="n">
+        <v>-108.971</v>
+      </c>
+      <c r="T138" s="12" t="n">
+        <v>-46.608</v>
+      </c>
+      <c r="U138" s="12" t="n">
+        <v>-56.634</v>
+      </c>
+      <c r="V138" s="12" t="n">
+        <v>435.58</v>
+      </c>
+      <c r="W138" s="12" t="n">
+        <v>-78.67100000000001</v>
+      </c>
+      <c r="X138" s="12" t="n">
+        <v>-108.971</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 환산차이</t>
         </is>
       </c>
-      <c r="C133" s="22" t="n">
+      <c r="C139" s="22" t="n">
         <v>12.24</v>
       </c>
-      <c r="E133" s="22" t="n">
+      <c r="E139" s="22" t="n">
         <v>27.755</v>
       </c>
-      <c r="G133" s="22" t="n">
+      <c r="G139" s="22" t="n">
         <v>-12.308</v>
       </c>
-      <c r="I133" s="22" t="n">
+      <c r="I139" s="22" t="n">
         <v>-62.808</v>
       </c>
-      <c r="K133" s="22" t="n">
+      <c r="K139" s="22" t="n">
         <v>29.503</v>
       </c>
-      <c r="M133" s="22" t="n">
+      <c r="M139" s="22" t="n">
         <v>39.882</v>
       </c>
-      <c r="T133" s="22" t="n">
+      <c r="T139" s="22" t="n">
         <v>11.913</v>
       </c>
-      <c r="U133" s="22" t="n">
+      <c r="U139" s="22" t="n">
         <v>8.737</v>
       </c>
-      <c r="V133" s="22" t="n">
+      <c r="V139" s="22" t="n">
         <v>27.755</v>
       </c>
-      <c r="W133" s="22" t="n">
+      <c r="W139" s="22" t="n">
         <v>-62.808</v>
       </c>
-      <c r="X133" s="22" t="n">
+      <c r="X139" s="22" t="n">
         <v>39.882</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="20" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="20" t="inlineStr">
         <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="C134" s="22" t="n">
+      <c r="C140" s="22" t="n">
         <v>553.558</v>
       </c>
-      <c r="E134" s="22" t="n">
+      <c r="E140" s="22" t="n">
         <v>1126.414</v>
       </c>
-      <c r="G134" s="22" t="n">
+      <c r="G140" s="22" t="n">
         <v>-214.734</v>
       </c>
-      <c r="I134" s="22" t="n">
+      <c r="I140" s="22" t="n">
         <v>327.984</v>
       </c>
-      <c r="K134" s="22" t="n">
+      <c r="K140" s="22" t="n">
         <v>124.911</v>
       </c>
-      <c r="M134" s="22" t="n">
+      <c r="M140" s="22" t="n">
         <v>-1562.167</v>
       </c>
-      <c r="T134" s="22" t="n">
+      <c r="T140" s="22" t="n">
         <v>423.152</v>
       </c>
-      <c r="U134" s="22" t="n">
+      <c r="U140" s="22" t="n">
         <v>526.794</v>
       </c>
-      <c r="V134" s="22" t="n">
+      <c r="V140" s="22" t="n">
         <v>1126.414</v>
       </c>
-      <c r="W134" s="22" t="n">
+      <c r="W140" s="22" t="n">
         <v>327.984</v>
       </c>
-      <c r="X134" s="22" t="n">
+      <c r="X140" s="22" t="n">
         <v>-1562.167</v>
       </c>
     </row>
@@ -7921,7 +8300,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -9309,7 +9688,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -9361,7 +9740,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -9413,7 +9792,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -9465,7 +9844,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -9517,7 +9896,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -9569,7 +9948,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -9621,7 +10000,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -9631,43 +10010,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -9691,7 +10070,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -9743,7 +10122,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -9795,7 +10174,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -9847,7 +10226,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -9899,7 +10278,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -9951,7 +10330,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -10021,7 +10400,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -10073,7 +10452,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -10083,49 +10462,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -10135,49 +10514,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -10187,49 +10566,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -10239,43 +10618,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -10299,7 +10678,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -10351,7 +10730,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -10403,7 +10782,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -10455,7 +10834,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -12199,767 +12578,767 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>지뎁어드밴스 섹터·사업 데이터</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="52" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>2단계 보고서를 만들 때 모은 자료 · 월차 · 출처는 맨 오른쪽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>가이던스 FY5 27</t>
         </is>
       </c>
-      <c r="B4" s="53" t="n"/>
-      <c r="C4" s="53" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="54" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C5" s="54" t="inlineStr">
+      <c r="C5" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B6" s="56" t="n">
+      <c r="B6" s="57" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="C6" s="57" t="inlineStr">
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
       </c>
-      <c r="B7" s="56" t="n">
+      <c r="B7" s="57" t="n">
         <v>12.68</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="55" t="inlineStr">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="B8" s="56" t="n">
+      <c r="B8" s="57" t="n">
         <v>8.289999999999999</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="55" t="inlineStr">
+      <c r="A9" s="56" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="B9" s="56" t="n">
+      <c r="B9" s="57" t="n">
         <v>150.83</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A10" s="56" t="inlineStr">
         <is>
           <t>dps</t>
         </is>
       </c>
-      <c r="B10" s="58" t="n">
+      <c r="B10" s="59" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="53" t="inlineStr">
+      <c r="A12" s="54" t="inlineStr">
         <is>
           <t>1Q slide · 영업이익 증감 요인</t>
         </is>
       </c>
-      <c r="B12" s="53" t="n"/>
-      <c r="C12" s="53" t="n"/>
+      <c r="B12" s="54" t="n"/>
+      <c r="C12" s="54" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="54" t="inlineStr">
+      <c r="A13" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B13" s="54" t="inlineStr">
+      <c r="B13" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C13" s="54" t="inlineStr">
+      <c r="C13" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="55" t="inlineStr">
+      <c r="A14" s="56" t="inlineStr">
         <is>
           <t>증수</t>
         </is>
       </c>
-      <c r="B14" s="56" t="n">
+      <c r="B14" s="57" t="n">
         <v>1.88</v>
       </c>
-      <c r="C14" s="57" t="inlineStr">
+      <c r="C14" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="55" t="inlineStr">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>매출총이익률</t>
         </is>
       </c>
-      <c r="B15" s="56" t="n">
+      <c r="B15" s="57" t="n">
         <v>0.62</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="55" t="inlineStr">
+      <c r="A16" s="56" t="inlineStr">
         <is>
           <t>인건비</t>
         </is>
       </c>
-      <c r="B16" s="56" t="n">
+      <c r="B16" s="57" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="55" t="inlineStr">
+      <c r="A17" s="56" t="inlineStr">
         <is>
           <t>업무위탁비</t>
         </is>
       </c>
-      <c r="B17" s="56" t="n">
+      <c r="B17" s="57" t="n">
         <v>-0.06</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="55" t="inlineStr">
+      <c r="A18" s="56" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="B18" s="56" t="n">
+      <c r="B18" s="57" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="53" t="inlineStr">
+      <c r="A20" s="54" t="inlineStr">
         <is>
           <t>1Q slide · industry mix 1Q 27</t>
         </is>
       </c>
-      <c r="B20" s="53" t="n"/>
-      <c r="C20" s="53" t="n"/>
+      <c r="B20" s="54" t="n"/>
+      <c r="C20" s="54" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="54" t="inlineStr">
+      <c r="A21" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B21" s="54" t="inlineStr">
+      <c r="B21" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C21" s="54" t="inlineStr">
+      <c r="C21" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="55" t="inlineStr">
+      <c r="A22" s="56" t="inlineStr">
         <is>
           <t>제조업</t>
         </is>
       </c>
-      <c r="B22" s="56" t="n">
+      <c r="B22" s="57" t="n">
         <v>35.2</v>
       </c>
-      <c r="C22" s="57" t="inlineStr">
+      <c r="C22" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="55" t="inlineStr">
+      <c r="A23" s="56" t="inlineStr">
         <is>
           <t>대학</t>
         </is>
       </c>
-      <c r="B23" s="56" t="n">
+      <c r="B23" s="57" t="n">
         <v>29.9</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="55" t="inlineStr">
+      <c r="A24" s="56" t="inlineStr">
         <is>
           <t>자동차</t>
         </is>
       </c>
-      <c r="B24" s="56" t="n">
+      <c r="B24" s="57" t="n">
         <v>11.5</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="55" t="inlineStr">
+      <c r="A25" s="56" t="inlineStr">
         <is>
           <t>스타트업</t>
         </is>
       </c>
-      <c r="B25" s="56" t="n">
+      <c r="B25" s="57" t="n">
         <v>7.2</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="55" t="inlineStr">
+      <c r="A26" s="56" t="inlineStr">
         <is>
           <t>정보통신</t>
         </is>
       </c>
-      <c r="B26" s="56" t="n">
+      <c r="B26" s="57" t="n">
         <v>4.6</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="55" t="inlineStr">
+      <c r="A27" s="56" t="inlineStr">
         <is>
           <t>의료</t>
         </is>
       </c>
-      <c r="B27" s="56" t="n">
+      <c r="B27" s="57" t="n">
         <v>3.2</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="53" t="inlineStr">
+      <c r="A29" s="54" t="inlineStr">
         <is>
           <t>1Q slide · industry mix 1Q 26</t>
         </is>
       </c>
-      <c r="B29" s="53" t="n"/>
-      <c r="C29" s="53" t="n"/>
+      <c r="B29" s="54" t="n"/>
+      <c r="C29" s="54" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="54" t="inlineStr">
+      <c r="A30" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B30" s="54" t="inlineStr">
+      <c r="B30" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C30" s="54" t="inlineStr">
+      <c r="C30" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="55" t="inlineStr">
+      <c r="A31" s="56" t="inlineStr">
         <is>
           <t>대학</t>
         </is>
       </c>
-      <c r="B31" s="56" t="n">
+      <c r="B31" s="57" t="n">
         <v>38.4</v>
       </c>
-      <c r="C31" s="57" t="inlineStr">
+      <c r="C31" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="55" t="inlineStr">
+      <c r="A32" s="56" t="inlineStr">
         <is>
           <t>제조업</t>
         </is>
       </c>
-      <c r="B32" s="56" t="n">
+      <c r="B32" s="57" t="n">
         <v>25.6</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="55" t="inlineStr">
+      <c r="A33" s="56" t="inlineStr">
         <is>
           <t>스타트업</t>
         </is>
       </c>
-      <c r="B33" s="56" t="n">
+      <c r="B33" s="57" t="n">
         <v>10.7</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="55" t="inlineStr">
+      <c r="A34" s="56" t="inlineStr">
         <is>
           <t>자동차</t>
         </is>
       </c>
-      <c r="B34" s="56" t="n">
+      <c r="B34" s="57" t="n">
         <v>6.1</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="53" t="inlineStr">
+      <c r="A36" s="54" t="inlineStr">
         <is>
           <t>bs · 상품재고</t>
         </is>
       </c>
-      <c r="B36" s="53" t="n"/>
-      <c r="C36" s="53" t="n"/>
+      <c r="B36" s="54" t="n"/>
+      <c r="C36" s="54" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="54" t="inlineStr">
+      <c r="A37" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B37" s="54" t="inlineStr">
+      <c r="B37" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C37" s="54" t="inlineStr">
+      <c r="C37" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="55" t="inlineStr">
+      <c r="A38" s="56" t="inlineStr">
         <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="B38" s="56" t="n">
+      <c r="B38" s="57" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="C38" s="57" t="inlineStr">
+      <c r="C38" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="55" t="inlineStr">
+      <c r="A39" s="56" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B39" s="56" t="n">
+      <c r="B39" s="57" t="n">
         <v>20.25</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="55" t="inlineStr">
+      <c r="A40" s="56" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B40" s="56" t="n">
+      <c r="B40" s="57" t="n">
         <v>20.54</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="53" t="inlineStr">
+      <c r="A42" s="54" t="inlineStr">
         <is>
           <t>bs · 선급금</t>
         </is>
       </c>
-      <c r="B42" s="53" t="n"/>
-      <c r="C42" s="53" t="n"/>
+      <c r="B42" s="54" t="n"/>
+      <c r="C42" s="54" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="54" t="inlineStr">
+      <c r="A43" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B43" s="54" t="inlineStr">
+      <c r="B43" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C43" s="54" t="inlineStr">
+      <c r="C43" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="55" t="inlineStr">
+      <c r="A44" s="56" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B44" s="56" t="n">
+      <c r="B44" s="57" t="n">
         <v>15.97</v>
       </c>
-      <c r="C44" s="57" t="inlineStr">
+      <c r="C44" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="55" t="inlineStr">
+      <c r="A45" s="56" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B45" s="56" t="n">
+      <c r="B45" s="57" t="n">
         <v>16.09</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="53" t="inlineStr">
+      <c r="A47" s="54" t="inlineStr">
         <is>
           <t>bs · 현금</t>
         </is>
       </c>
-      <c r="B47" s="53" t="n"/>
-      <c r="C47" s="53" t="n"/>
+      <c r="B47" s="54" t="n"/>
+      <c r="C47" s="54" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="54" t="inlineStr">
+      <c r="A48" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B48" s="54" t="inlineStr">
+      <c r="B48" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C48" s="54" t="inlineStr">
+      <c r="C48" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="55" t="inlineStr">
+      <c r="A49" s="56" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B49" s="56" t="n">
+      <c r="B49" s="57" t="n">
         <v>17.71</v>
       </c>
-      <c r="C49" s="57" t="inlineStr">
+      <c r="C49" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="55" t="inlineStr">
+      <c r="A50" s="56" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B50" s="56" t="n">
+      <c r="B50" s="57" t="n">
         <v>14.87</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="53" t="inlineStr">
+      <c r="A52" s="54" t="inlineStr">
         <is>
           <t>PER band ttm</t>
         </is>
       </c>
-      <c r="B52" s="53" t="n"/>
-      <c r="C52" s="53" t="n"/>
+      <c r="B52" s="54" t="n"/>
+      <c r="C52" s="54" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="54" t="inlineStr">
+      <c r="A53" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B53" s="54" t="inlineStr">
+      <c r="B53" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C53" s="54" t="inlineStr">
+      <c r="C53" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="55" t="inlineStr">
+      <c r="A54" s="56" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="B54" s="56" t="n">
+      <c r="B54" s="57" t="n">
         <v>16.5</v>
       </c>
-      <c r="C54" s="57" t="inlineStr">
+      <c r="C54" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="55" t="inlineStr">
+      <c r="A55" s="56" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="B55" s="56" t="n">
+      <c r="B55" s="57" t="n">
         <v>34.4</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="55" t="inlineStr">
+      <c r="A56" s="56" t="inlineStr">
         <is>
           <t>avg</t>
         </is>
       </c>
-      <c r="B56" s="56" t="n">
+      <c r="B56" s="57" t="n">
         <v>24.8</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="55" t="inlineStr">
+      <c r="A57" s="56" t="inlineStr">
         <is>
           <t>now</t>
         </is>
       </c>
-      <c r="B57" s="56" t="n">
+      <c r="B57" s="57" t="n">
         <v>19.5</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="55" t="inlineStr">
+      <c r="A58" s="56" t="inlineStr">
         <is>
           <t>pos %</t>
         </is>
       </c>
-      <c r="B58" s="58" t="n">
+      <c r="B58" s="59" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="53" t="inlineStr">
+      <c r="A60" s="54" t="inlineStr">
         <is>
           <t>peers · 6597 HPC시스템즈 (6월 결산, 다음 11/13)</t>
         </is>
       </c>
-      <c r="B60" s="53" t="n"/>
-      <c r="C60" s="53" t="n"/>
+      <c r="B60" s="54" t="n"/>
+      <c r="C60" s="54" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="54" t="inlineStr">
+      <c r="A61" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B61" s="54" t="inlineStr">
+      <c r="B61" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C61" s="54" t="inlineStr">
+      <c r="C61" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="55" t="inlineStr">
+      <c r="A62" s="56" t="inlineStr">
         <is>
           <t>guid EPS</t>
         </is>
       </c>
-      <c r="B62" s="56" t="n">
+      <c r="B62" s="57" t="n">
         <v>162.74</v>
       </c>
-      <c r="C62" s="57" t="inlineStr">
+      <c r="C62" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="55" t="inlineStr">
+      <c r="A63" s="56" t="inlineStr">
         <is>
           <t>가격</t>
         </is>
       </c>
-      <c r="B63" s="58" t="n">
+      <c r="B63" s="59" t="n">
         <v>3080</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="55" t="inlineStr">
+      <c r="A64" s="56" t="inlineStr">
         <is>
           <t>1y</t>
         </is>
       </c>
-      <c r="B64" s="56" t="n">
+      <c r="B64" s="57" t="n">
         <v>65.59999999999999</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="53" t="inlineStr">
+      <c r="A66" s="54" t="inlineStr">
         <is>
           <t>peers · 3778 사쿠라인터넷 (3월 결산, 다음 10/28)</t>
         </is>
       </c>
-      <c r="B66" s="53" t="n"/>
-      <c r="C66" s="53" t="n"/>
+      <c r="B66" s="54" t="n"/>
+      <c r="C66" s="54" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="54" t="inlineStr">
+      <c r="A67" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B67" s="54" t="inlineStr">
+      <c r="B67" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C67" s="54" t="inlineStr">
+      <c r="C67" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="55" t="inlineStr">
+      <c r="A68" s="56" t="inlineStr">
         <is>
           <t>guid EPS</t>
         </is>
       </c>
-      <c r="B68" s="56" t="n">
+      <c r="B68" s="57" t="n">
         <v>37.46</v>
       </c>
-      <c r="C68" s="57" t="inlineStr">
+      <c r="C68" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="55" t="inlineStr">
+      <c r="A69" s="56" t="inlineStr">
         <is>
           <t>가격</t>
         </is>
       </c>
-      <c r="B69" s="58" t="n">
+      <c r="B69" s="59" t="n">
         <v>2936</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="55" t="inlineStr">
+      <c r="A70" s="56" t="inlineStr">
         <is>
           <t>1y</t>
         </is>
       </c>
-      <c r="B70" s="56" t="n">
+      <c r="B70" s="57" t="n">
         <v>-14.4</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="53" t="inlineStr">
+      <c r="A72" s="54" t="inlineStr">
         <is>
           <t>peers · 3687 픽스타즈 (9월 결산, 다음 11/6)</t>
         </is>
       </c>
-      <c r="B72" s="53" t="n"/>
-      <c r="C72" s="53" t="n"/>
+      <c r="B72" s="54" t="n"/>
+      <c r="C72" s="54" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="54" t="inlineStr">
+      <c r="A73" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B73" s="54" t="inlineStr">
+      <c r="B73" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C73" s="54" t="inlineStr">
+      <c r="C73" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="55" t="inlineStr">
+      <c r="A74" s="56" t="inlineStr">
         <is>
           <t>guid EPS</t>
         </is>
       </c>
-      <c r="B74" s="56" t="n">
+      <c r="B74" s="57" t="n">
         <v>60.39</v>
       </c>
-      <c r="C74" s="57" t="inlineStr">
+      <c r="C74" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="55" t="inlineStr">
+      <c r="A75" s="56" t="inlineStr">
         <is>
           <t>가격</t>
         </is>
       </c>
-      <c r="B75" s="58" t="n">
+      <c r="B75" s="59" t="n">
         <v>1872</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="55" t="inlineStr">
+      <c r="A76" s="56" t="inlineStr">
         <is>
           <t>1y</t>
         </is>
       </c>
-      <c r="B76" s="56" t="n">
+      <c r="B76" s="57" t="n">
         <v>-2.8</v>
       </c>
     </row>
@@ -12983,24 +13362,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="59" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="59" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
